--- a/data/trans_orig/IP3110_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP3110_2023-Estudios-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>414</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>5589</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,47 +780,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>9,58%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2714</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>775</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6766</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>8,67%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2714</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>840</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6976</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19084</t>
+          <t>18509</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>5046</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15881</t>
+          <t>15477</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12113</t>
+          <t>11847</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29097</t>
+          <t>28910</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14206</t>
+          <t>14976</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33452</t>
+          <t>34080</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14546</t>
+          <t>14851</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28291</t>
+          <t>28642</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33741</t>
+          <t>33210</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56998</t>
+          <t>56391</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>50,56%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16087</t>
+          <t>15627</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19643</t>
+          <t>19421</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15701</t>
+          <t>15856</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31007</t>
+          <t>32107</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,79%</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2258</t>
+          <t>2403</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14677</t>
+          <t>13840</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>8555</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21447</t>
+          <t>20932</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7835</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2477</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>9890</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15337</t>
+          <t>14983</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18723</t>
+          <t>18117</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35316</t>
+          <t>34890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18981</t>
+          <t>18701</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39683</t>
+          <t>38305</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42316</t>
+          <t>42326</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66567</t>
+          <t>69292</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>58702</t>
+          <t>58790</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>90804</t>
+          <t>89620</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51128</t>
+          <t>51397</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>79836</t>
+          <t>80374</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>117830</t>
+          <t>120221</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>161093</t>
+          <t>161054</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>142073</t>
+          <t>141445</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>194372</t>
+          <t>194943</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>189014</t>
+          <t>188523</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>236058</t>
+          <t>236240</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>343952</t>
+          <t>340653</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>418503</t>
+          <t>417236</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,83%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84654</t>
+          <t>86965</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>172080</t>
+          <t>180891</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>98031</t>
+          <t>97518</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>152030</t>
+          <t>146010</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>195139</t>
+          <t>195431</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>301788</t>
+          <t>309346</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40621</t>
+          <t>39960</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66180</t>
+          <t>65126</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>55256</t>
+          <t>54364</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>90953</t>
+          <t>89134</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>102399</t>
+          <t>100013</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>144633</t>
+          <t>143657</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14668</t>
+          <t>15451</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6329</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19839</t>
+          <t>19431</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13853</t>
+          <t>13913</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29072</t>
+          <t>30158</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19996</t>
+          <t>20508</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9435</t>
+          <t>9693</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23852</t>
+          <t>24093</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>21140</t>
+          <t>21724</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39644</t>
+          <t>39602</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26160</t>
+          <t>26249</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42569</t>
+          <t>42814</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41367</t>
+          <t>41341</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64534</t>
+          <t>63240</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>71828</t>
+          <t>71745</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>100286</t>
+          <t>99954</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61547</t>
+          <t>61770</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>81962</t>
+          <t>81303</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62515</t>
+          <t>62126</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>86367</t>
+          <t>87381</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>128476</t>
+          <t>130510</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>160047</t>
+          <t>161658</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>49,39%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13165</t>
+          <t>13392</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26948</t>
+          <t>26045</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21729</t>
+          <t>21732</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42490</t>
+          <t>43799</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>38714</t>
+          <t>38737</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>63537</t>
+          <t>63864</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12315</t>
+          <t>11849</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12770</t>
+          <t>13069</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8402</t>
+          <t>8442</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21605</t>
+          <t>21359</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>5813</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9436</t>
+          <t>8611</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30850</t>
+          <t>30963</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51132</t>
+          <t>52966</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34604</t>
+          <t>34591</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59097</t>
+          <t>59053</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>70984</t>
+          <t>71700</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>101942</t>
+          <t>103341</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>99880</t>
+          <t>99123</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>139433</t>
+          <t>138249</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>107056</t>
+          <t>107952</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>146086</t>
+          <t>147416</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>217527</t>
+          <t>219063</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>269784</t>
+          <t>270737</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>230146</t>
+          <t>229002</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>293783</t>
+          <t>293570</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>280156</t>
+          <t>278181</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>333335</t>
+          <t>336364</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>532419</t>
+          <t>529980</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>611722</t>
+          <t>620283</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>44,6%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>113814</t>
+          <t>114273</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>213781</t>
+          <t>214249</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>138523</t>
+          <t>136519</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>192477</t>
+          <t>191386</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>264226</t>
+          <t>262752</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>368616</t>
+          <t>377794</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>52419</t>
+          <t>51244</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>79516</t>
+          <t>77881</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>69896</t>
+          <t>68306</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>105842</t>
+          <t>105084</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>129705</t>
+          <t>128340</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>173309</t>
+          <t>176071</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9058</t>
+          <t>9512</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22543</t>
+          <t>21634</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12133</t>
+          <t>12878</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>27942</t>
+          <t>28043</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>24712</t>
+          <t>24553</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>44205</t>
+          <t>44020</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP3110_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP3110_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1732</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5694</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,6%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4632</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3987</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,71%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1899</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5589</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2714</t>
+          <t>2422</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>608</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6766</t>
+          <t>6226</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8218</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4466</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13757</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>15,3%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8,31%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>25,61%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9773</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4491</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18509</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>18,38%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>34,81%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9090</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5046</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15477</t>
+          <t>14080</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>18864</t>
+          <t>16708</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11847</t>
+          <t>11064</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28910</t>
+          <t>23255</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18257</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12612</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>25048</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>33,99%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>23,48%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>46,63%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>22887</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>14976</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>34080</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>43,04%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>28,16%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>64,09%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20952</t>
+          <t>16048</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14851</t>
+          <t>10901</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28642</t>
+          <t>22135</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>43839</t>
+          <t>34305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33210</t>
+          <t>27000</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56391</t>
+          <t>43572</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>43,93%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11993</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6793</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18628</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>22,33%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12,65%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>34,68%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10130</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5950</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>15627</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>19,05%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>11,19%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>29,39%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12695</t>
+          <t>10045</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7781</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19421</t>
+          <t>15098</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>22825</t>
+          <t>22037</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15856</t>
+          <t>15287</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32107</t>
+          <t>29213</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8238</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4339</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14086</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>15,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>8,08%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>26,22%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5727</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2403</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10898</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,77%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>20,49%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4245</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13840</t>
+          <t>10856</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>13972</t>
+          <t>14339</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8555</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20932</t>
+          <t>21360</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -1285,72 +1285,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5277</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2342</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>9583</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>9,82%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>17,84%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>3845</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1503</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>8086</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>15,2%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9890</t>
+          <t>8982</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>9309</t>
+          <t>9372</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5454</t>
+          <t>4878</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14983</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -1398,74 +1398,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>53177</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>53177</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>53177</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>45468</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>45468</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>45468</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>58345</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>58345</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>58345</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>143</t>
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>111522</t>
+          <t>99183</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111522</t>
+          <t>99183</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111522</t>
+          <t>99183</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>22046</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>15695</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>32113</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>6,89%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>26000</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>18117</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>34890</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>7,78%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27369</t>
+          <t>24539</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18701</t>
+          <t>17712</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38305</t>
+          <t>33481</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>53369</t>
+          <t>46585</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42326</t>
+          <t>36647</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69292</t>
+          <t>57730</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>59556</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>48383</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>74689</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>12,78%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>10,39%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>16,03%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>74875</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>58790</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>89620</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>13,11%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>19,98%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>65494</t>
+          <t>74140</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51397</t>
+          <t>62633</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>80374</t>
+          <t>90140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>140370</t>
+          <t>133696</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120221</t>
+          <t>117747</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>161054</t>
+          <t>152882</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>194623</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>173080</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>216753</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>41,78%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>37,15%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>46,53%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>173759</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>141445</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>194943</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>38,74%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>31,54%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>43,47%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>212153</t>
+          <t>170973</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>188523</t>
+          <t>155570</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>236240</t>
+          <t>189196</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>385912</t>
+          <t>365596</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>340653</t>
+          <t>336661</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>417236</t>
+          <t>389607</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,92%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>109177</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>91181</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>132470</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>23,44%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>19,57%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>28,44%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>112444</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>86965</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>180891</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>25,07%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>19,39%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>40,33%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>117224</t>
+          <t>88199</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>97518</t>
+          <t>74732</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>146010</t>
+          <t>103981</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>229668</t>
+          <t>197377</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>195431</t>
+          <t>175097</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>309346</t>
+          <t>227089</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -1967,72 +1967,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>68825</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>54354</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>87490</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>14,77%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>11,67%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>18,78%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>52145</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>39960</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>65126</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>11,63%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>8,91%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>14,52%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>69648</t>
+          <t>54472</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>54364</t>
+          <t>43254</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>89134</t>
+          <t>68191</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>121793</t>
+          <t>123297</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>100013</t>
+          <t>103908</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>143657</t>
+          <t>144455</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -2080,107 +2080,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11634</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6040</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>18890</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,05%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>9257</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5366</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15451</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11650</t>
+          <t>8891</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19431</t>
+          <t>14676</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>3,48%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>20525</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>13581</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>29410</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>2,31%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>20907</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>13913</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>30158</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -2193,74 +2193,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>465861</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>465861</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>465861</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>622</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>448480</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>448480</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>448480</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>421214</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>421214</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>421214</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>629</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>503539</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>503539</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>503539</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1251</t>
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>952019</t>
+          <t>887076</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>952019</t>
+          <t>887076</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>952019</t>
+          <t>887076</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>14173</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8810</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>20972</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>5,29%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>12,58%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>13558</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>8362</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>20508</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,72%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>14,03%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15766</t>
+          <t>12527</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9693</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24093</t>
+          <t>19508</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>29324</t>
+          <t>26701</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>21724</t>
+          <t>18235</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39602</t>
+          <t>35414</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>46968</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>37377</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>58863</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>28,18%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>22,42%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>35,31%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>33933</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>26249</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>42814</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>23,21%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>17,96%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>29,29%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>51263</t>
+          <t>33728</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41341</t>
+          <t>26035</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63240</t>
+          <t>42071</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>85196</t>
+          <t>80695</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>71745</t>
+          <t>67005</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>99954</t>
+          <t>93412</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>29,77%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>70028</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>59378</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>82133</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>42,01%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>35,62%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>49,27%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>71200</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>61770</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>81303</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>48,71%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>42,25%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>55,62%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>74504</t>
+          <t>72737</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62126</t>
+          <t>63084</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>87381</t>
+          <t>82975</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>145704</t>
+          <t>142765</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>130510</t>
+          <t>128349</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>161658</t>
+          <t>158775</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>50,59%</t>
         </is>
       </c>
     </row>
@@ -2649,72 +2649,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>25824</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>18680</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>35279</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>15,49%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>11,21%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>21,16%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>19234</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>13392</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>26045</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>13,16%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>9,16%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>17,82%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30328</t>
+          <t>19387</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21732</t>
+          <t>13066</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>43799</t>
+          <t>27233</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>49562</t>
+          <t>45211</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>38737</t>
+          <t>35368</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>63864</t>
+          <t>56056</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -2762,72 +2762,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>7864</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3857</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>13868</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>4,72%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>8,32%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>6544</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>3521</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>11849</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>8,11%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13069</t>
+          <t>12977</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>13859</t>
+          <t>14784</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8442</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21359</t>
+          <t>22672</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -2875,107 +2875,107 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>5603</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1841</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>6343</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>6793</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>3670</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1256</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>8799</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>4,34%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>1964</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>5813</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>3681</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1237</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>8611</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -2988,74 +2988,74 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>147140</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>147140</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>147140</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>181139</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>181139</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>181139</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>455</t>
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>37952</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>29225</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>50485</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>7,36%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>40373</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>30963</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>52966</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>6,23%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>45033</t>
+          <t>37756</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34591</t>
+          <t>28938</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59053</t>
+          <t>48309</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>85406</t>
+          <t>75708</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>71700</t>
+          <t>62904</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>103341</t>
+          <t>91278</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>114742</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>96436</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>133940</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>16,72%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>14,05%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>19,52%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>118582</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>99123</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>138249</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>18,3%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>15,3%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>21,34%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>125847</t>
+          <t>116358</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>107952</t>
+          <t>100668</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>147416</t>
+          <t>132565</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>244429</t>
+          <t>231099</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>219063</t>
+          <t>207608</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>270737</t>
+          <t>254765</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -3331,72 +3331,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>282909</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>257184</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>307842</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>41,22%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>37,48%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>44,86%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>385</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>267846</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>229002</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>293570</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>41,34%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>35,35%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>45,32%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>387</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>307608</t>
+          <t>259757</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>278181</t>
+          <t>239062</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>336364</t>
+          <t>281694</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>575455</t>
+          <t>542665</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>529980</t>
+          <t>510479</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>620283</t>
+          <t>576938</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,38%</t>
         </is>
       </c>
     </row>
@@ -3444,72 +3444,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>146995</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>126823</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>174502</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>21,42%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>18,48%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>25,43%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>141807</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>114273</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>214249</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>21,89%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>17,64%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>33,07%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>160247</t>
+          <t>117631</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>136519</t>
+          <t>101956</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>191386</t>
+          <t>136181</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>302054</t>
+          <t>264625</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>262752</t>
+          <t>236293</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>377794</t>
+          <t>294629</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -3557,72 +3557,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>84926</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>69817</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>105762</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>12,38%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>10,17%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>15,41%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>64416</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>51244</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>77881</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>9,94%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>12,02%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>85208</t>
+          <t>67493</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>68306</t>
+          <t>56051</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>105084</t>
+          <t>82484</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>149624</t>
+          <t>152419</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>128340</t>
+          <t>130899</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>176071</t>
+          <t>176326</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -3670,72 +3670,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>18739</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>27125</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>14818</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>9512</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>21634</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>19078</t>
+          <t>14827</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12878</t>
+          <t>9253</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>28043</t>
+          <t>22747</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>33897</t>
+          <t>33566</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>24553</t>
+          <t>24103</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>44020</t>
+          <t>43641</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -3783,74 +3783,74 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>686262</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>686262</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>686262</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>910</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>647843</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>647843</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>647843</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>613822</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>613822</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>613822</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>743022</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>743022</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>743022</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>1849</t>
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1390865</t>
+          <t>1300083</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1390865</t>
+          <t>1300083</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1390865</t>
+          <t>1300083</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
